--- a/nr-fix-template-2/ig/CdaIVL-TSToPeriodConceptMap.xlsx
+++ b/nr-fix-template-2/ig/CdaIVL-TSToPeriodConceptMap.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:55:27+00:00</t>
+    <t>2026-06-16T12:00:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
